--- a/roster_db.xlsx
+++ b/roster_db.xlsx
@@ -568,7 +568,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nord</t>
+          <t>North</t>
         </is>
       </c>
     </row>
